--- a/测试集/泛用性验收_v3/W2/W2_反馈_财务部.xlsx
+++ b/测试集/泛用性验收_v3/W2/W2_反馈_财务部.xlsx
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="C2" t="n">
         <v>99</v>

--- a/测试集/泛用性验收_v3/W2/W2_反馈_财务部.xlsx
+++ b/测试集/泛用性验收_v3/W2/W2_反馈_财务部.xlsx
@@ -525,7 +525,7 @@
         <v>99</v>
       </c>
       <c r="C2" t="n">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="D2" t="n">
         <v>25</v>
